--- a/src/test/resources/Data.xlsx
+++ b/src/test/resources/Data.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="8400" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -50,13 +50,13 @@
     <t>2k22aids24@kiot.ac.in</t>
   </si>
   <si>
-    <t>titoo123</t>
+    <t>titoo</t>
   </si>
   <si>
     <t>titooram123@gmail.com</t>
   </si>
   <si>
-    <t>sriram123</t>
+    <t>sriram</t>
   </si>
   <si>
     <t>validSearch</t>
@@ -1270,7 +1270,7 @@
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B3" t="s">
